--- a/Gain Sheet.xlsx
+++ b/Gain Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KUSH\ArtixMix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F2736C2-1628-4AA6-955E-DDDDDBCF0D43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D968A580-A7A7-4540-A3B4-A45EA15C3F47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{162F6800-650B-40DC-87AA-5313FF53ABEB}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
   <si>
     <t>Amplitude Ratio</t>
   </si>
@@ -102,6 +102,9 @@
   </si>
   <si>
     <t>Output</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error </t>
   </si>
 </sst>
 </file>
@@ -475,7 +478,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30640A05-FE0D-4691-B386-01EF647E2A68}">
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" bestFit="1" customWidth="1"/>
@@ -489,7 +492,7 @@
     <col min="11" max="11" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -520,8 +523,11 @@
       <c r="K1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="M1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>-6</v>
       </c>
@@ -554,8 +560,12 @@
         <f>J2/I2</f>
         <v>0.5009765625</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="M2">
+        <f>(K2-B2)*100/B2</f>
+        <v>-4.4580506783714856E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>-5</v>
       </c>
@@ -585,11 +595,15 @@
         <v>2303</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K17" si="1">J3/I3</f>
+        <f t="shared" ref="K3:K14" si="1">J3/I3</f>
         <v>0.562255859375</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="M3">
+        <f t="shared" ref="M3:M14" si="2">(K3-B3)*100/B3</f>
+        <v>-7.8500133380796765E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>-4</v>
       </c>
@@ -622,8 +636,12 @@
         <f t="shared" si="1"/>
         <v>0.630859375</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="M4">
+        <f t="shared" si="2"/>
+        <v>-2.2286053882726677E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>-3</v>
       </c>
@@ -656,8 +674,12 @@
         <f t="shared" si="1"/>
         <v>0.707763671875</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="M5">
+        <f t="shared" si="2"/>
+        <v>-1.9258104958323734E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>-2</v>
       </c>
@@ -684,14 +706,18 @@
         <v>4096</v>
       </c>
       <c r="J6">
-        <v>2899</v>
+        <v>3253</v>
       </c>
       <c r="K6">
         <f t="shared" si="1"/>
-        <v>0.707763671875</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0.794189453125</v>
+      </c>
+      <c r="M6">
+        <f t="shared" si="2"/>
+        <v>-1.3917521717236063E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>-1</v>
       </c>
@@ -712,20 +738,24 @@
         <v>29206</v>
       </c>
       <c r="H7">
-        <v>1576</v>
+        <v>1891</v>
       </c>
       <c r="I7">
         <v>4096</v>
       </c>
       <c r="J7">
-        <v>3253</v>
+        <v>3634</v>
       </c>
       <c r="K7">
         <f t="shared" si="1"/>
-        <v>0.794189453125</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0.88720703125</v>
+      </c>
+      <c r="M7">
+        <f t="shared" si="2"/>
+        <v>-0.45921336811398872</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>0</v>
       </c>
@@ -746,20 +776,24 @@
         <v>32768</v>
       </c>
       <c r="H8">
-        <v>1891</v>
+        <v>2206</v>
       </c>
       <c r="I8">
         <v>4096</v>
       </c>
       <c r="J8">
-        <v>3634</v>
+        <v>4096</v>
       </c>
       <c r="K8">
         <f t="shared" si="1"/>
-        <v>0.88720703125</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1</v>
       </c>
@@ -773,27 +807,31 @@
         <v>9</v>
       </c>
       <c r="E9">
-        <f t="shared" ref="E9:E14" si="2">B9*32768</f>
+        <f t="shared" ref="E9:E14" si="3">B9*32768</f>
         <v>36765.696000000004</v>
       </c>
       <c r="F9">
         <v>36766</v>
       </c>
       <c r="H9">
-        <v>2206</v>
+        <v>2521</v>
       </c>
       <c r="I9">
         <v>4096</v>
       </c>
       <c r="J9">
-        <v>4096</v>
+        <v>4603</v>
       </c>
       <c r="K9">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+        <v>1.123779296875</v>
+      </c>
+      <c r="M9">
+        <f t="shared" si="2"/>
+        <v>0.15858260918002598</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2</v>
       </c>
@@ -807,27 +845,31 @@
         <v>10</v>
       </c>
       <c r="E10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>41251.635199999997</v>
       </c>
       <c r="F10">
         <v>41252</v>
       </c>
       <c r="H10">
-        <v>2521</v>
+        <v>2836</v>
       </c>
       <c r="I10">
         <v>4096</v>
       </c>
       <c r="J10">
-        <v>4603</v>
+        <v>5156</v>
       </c>
       <c r="K10">
         <f t="shared" si="1"/>
-        <v>1.123779296875</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+        <v>1.2587890625</v>
+      </c>
+      <c r="M10">
+        <f t="shared" si="2"/>
+        <v>-8.8122567320603699E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>3</v>
       </c>
@@ -841,27 +883,31 @@
         <v>11</v>
       </c>
       <c r="E11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>46284.800000000003</v>
       </c>
       <c r="F11">
         <v>46285</v>
       </c>
       <c r="H11">
-        <v>2836</v>
+        <v>3150</v>
       </c>
       <c r="I11">
         <v>4096</v>
       </c>
       <c r="J11">
-        <v>4603</v>
+        <v>5793</v>
       </c>
       <c r="K11">
         <f t="shared" si="1"/>
-        <v>1.123779296875</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+        <v>1.414306640625</v>
+      </c>
+      <c r="M11">
+        <f t="shared" si="2"/>
+        <v>0.1279037610619406</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>4</v>
       </c>
@@ -875,27 +921,31 @@
         <v>12</v>
       </c>
       <c r="E12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>51934.003199999999</v>
       </c>
       <c r="F12">
         <v>51934</v>
       </c>
       <c r="H12">
-        <v>2836</v>
+        <v>3466</v>
       </c>
       <c r="I12">
         <v>4096</v>
       </c>
       <c r="J12">
-        <v>5156</v>
+        <v>6491</v>
       </c>
       <c r="K12">
         <f t="shared" si="1"/>
-        <v>1.2587890625</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+        <v>1.584716796875</v>
+      </c>
+      <c r="M12">
+        <f t="shared" si="2"/>
+        <v>-1.1559286074829674E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>5</v>
       </c>
@@ -909,27 +959,31 @@
         <v>13</v>
       </c>
       <c r="E13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>58271.3344</v>
       </c>
       <c r="F13">
         <v>58271</v>
       </c>
       <c r="H13">
-        <v>3150</v>
+        <v>3781</v>
       </c>
       <c r="I13">
         <v>4096</v>
       </c>
       <c r="J13">
-        <v>5793</v>
+        <v>7283</v>
       </c>
       <c r="K13">
         <f t="shared" si="1"/>
-        <v>1.414306640625</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+        <v>1.778076171875</v>
+      </c>
+      <c r="M13">
+        <f t="shared" si="2"/>
+        <v>-1.258663470730427E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>6</v>
       </c>
@@ -943,69 +997,28 @@
         <v>14</v>
       </c>
       <c r="E14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>65381.990400000002</v>
       </c>
       <c r="F14">
         <v>65382</v>
       </c>
       <c r="H14">
-        <v>3466</v>
+        <v>4095</v>
       </c>
       <c r="I14">
         <v>4096</v>
       </c>
       <c r="J14">
-        <v>6491</v>
+        <v>8172</v>
       </c>
       <c r="K14">
         <f t="shared" si="1"/>
-        <v>1.584716796875</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="H15">
-        <v>3781</v>
-      </c>
-      <c r="I15">
-        <v>4096</v>
-      </c>
-      <c r="J15">
-        <v>7283</v>
-      </c>
-      <c r="K15">
-        <f t="shared" si="1"/>
-        <v>1.778076171875</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="H16">
-        <v>4095</v>
-      </c>
-      <c r="I16">
-        <v>4096</v>
-      </c>
-      <c r="J16">
-        <v>7283</v>
-      </c>
-      <c r="K16">
-        <f t="shared" si="1"/>
-        <v>1.778076171875</v>
-      </c>
-    </row>
-    <row r="17" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H17">
-        <v>4095</v>
-      </c>
-      <c r="I17">
-        <v>4096</v>
-      </c>
-      <c r="J17">
-        <v>8172</v>
-      </c>
-      <c r="K17">
-        <f t="shared" si="1"/>
         <v>1.9951171875</v>
+      </c>
+      <c r="M14">
+        <f t="shared" si="2"/>
+        <v>-9.1621560667605635E-3</v>
       </c>
     </row>
   </sheetData>
